--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-integration-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-integration-easy.xlsx
@@ -463,13 +463,13 @@
         <v>Application Programming Interface — Giao diện lập trình ứng dụng cho phép hai hệ thống phần mềm giao tiếp và trao đổi dữ liệu với nhau — cầu nối giao tiếp</v>
       </c>
       <c r="G2" t="str">
+        <v>Advanced Program Instruction — Tập lệnh nâng cao dùng để điều khiển card đồ họa máy tính — tập lệnh card màn hình</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Automated Product Index — Chỉ số sản phẩm tự động hiển thị trên website bán hàng thương mại điện tử — chỉ số sản phẩm</v>
+      </c>
+      <c r="I2" t="str">
         <v>Active Process Integration — Quy trình tích hợp các tiến trình đang chạy trên bộ nhớ RAM của máy chủ — quy trình bộ nhớ</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Advanced Program Instruction — Tập lệnh nâng cao dùng để điều khiển card đồ họa máy tính — tập lệnh card màn hình</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Automated Product Index — Chỉ số sản phẩm tự động hiển thị trên website bán hàng thương mại điện tử — chỉ số sản phẩm</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>JSON là định dạng dữ liệu dạng text nhẹ, sử dụng cặp key-value (tương tự như object của Javascript), là định dạng trao đổi dữ liệu phổ biến nhất hiện nay qua API.</v>
       </c>
       <c r="F3" t="str">
-        <v>Định dạng văn bản gọn nhẹ, dễ đọc viết đối với con người và dễ phân tích đối với máy tính dưới dạng key-value — định dạng key-value gọn nhẹ</v>
+        <v>Định dạng bảng tính Excel chứa các ô dữ liệu được ngăn cách bằng dấu phẩy — bảng tính CSV</v>
       </c>
       <c r="G3" t="str">
         <v>Định dạng mã hóa nhị phân phức tạp chỉ có bộ vi xử lý máy tính mới đọc hiểu được — mã hóa nhị phân</v>
       </c>
       <c r="H3" t="str">
-        <v>Định dạng bảng tính Excel chứa các ô dữ liệu được ngăn cách bằng dấu phẩy — bảng tính CSV</v>
+        <v>Ngôn ngữ đánh dấu siêu văn bản dùng để thiết kế màu sắc cho giao diện trang web — ngôn ngữ giao diện HTML</v>
       </c>
       <c r="I3" t="str">
-        <v>Ngôn ngữ đánh dấu siêu văn bản dùng để thiết kế màu sắc cho giao diện trang web — ngôn ngữ giao diện HTML</v>
+        <v>Định dạng văn bản gọn nhẹ, dễ đọc viết đối với con người và dễ phân tích đối với máy tính dưới dạng key-value — định dạng key-value gọn nhẹ</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>ERD là sơ đồ mối quan hệ thực thể, biểu diễn cấu trúc dữ liệu logic của hệ thống bằng các thực thể, thuộc tính và liên kết (1-1, 1-n, n-n) giữa chúng.</v>
       </c>
       <c r="F4" t="str">
-        <v>Các thực thể dữ liệu, các thuộc tính của chúng và mối quan hệ giữa các thực thể đó — sơ đồ mối quan hệ thực thể</v>
+        <v>Luồng đi của dữ liệu qua các tiến trình xử lý và nơi lưu trữ dữ liệu — sơ đồ luồng dữ liệu DFD</v>
       </c>
       <c r="G4" t="str">
-        <v>Luồng đi của dữ liệu qua các tiến trình xử lý và nơi lưu trữ dữ liệu — sơ đồ luồng dữ liệu DFD</v>
+        <v>Giao diện người dùng của các form đăng ký thông tin khách hàng — giao diện nhập liệu</v>
       </c>
       <c r="H4" t="str">
         <v>Thời gian phản hồi trung bình của cơ sở dữ liệu khi chạy truy vấn nặng — hiệu năng database</v>
       </c>
       <c r="I4" t="str">
-        <v>Giao diện người dùng của các form đăng ký thông tin khách hàng — giao diện nhập liệu</v>
+        <v>Các thực thể dữ liệu, các thuộc tính của chúng và mối quan hệ giữa các thực thể đó — sơ đồ mối quan hệ thực thể</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Theo chuẩn RESTful, POST dùng để gửi dữ liệu lên server để tạo mới tài nguyên (ví dụ: tạo mới đơn hàng, tài khoản).</v>
       </c>
       <c r="F5" t="str">
+        <v>GET — dùng để truy xuất và lấy dữ liệu từ máy chủ về hệ thống — lấy dữ liệu</v>
+      </c>
+      <c r="G5" t="str">
+        <v>DELETE — dùng để xóa bỏ một tài nguyên đang lưu trữ trên máy chủ — xóa dữ liệu</v>
+      </c>
+      <c r="H5" t="str">
         <v>POST — dùng để tạo mới một tài nguyên hoặc gửi dữ liệu lên máy chủ — tạo mới tài nguyên</v>
-      </c>
-      <c r="G5" t="str">
-        <v>GET — dùng để truy xuất và lấy dữ liệu từ máy chủ về hệ thống — lấy dữ liệu</v>
-      </c>
-      <c r="H5" t="str">
-        <v>DELETE — dùng để xóa bỏ một tài nguyên đang lưu trữ trên máy chủ — xóa dữ liệu</v>
       </c>
       <c r="I5" t="str">
         <v>HEAD — dùng để kiểm tra thông tin tiêu đề header của API mà không lấy dữ liệu — kiểm tra header</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>XML sử dụng cấu trúc cây với các tag mở/đóng tự định nghĩa để lưu trữ dữ liệu. So với JSON, XML dài dòng và tốn băng thông truyền tải hơn.</v>
       </c>
       <c r="F6" t="str">
-        <v>Sử dụng các cặp thẻ lồng nhau (như &lt;the&gt;noi dung&lt;/the&gt;) để cấu trúc dữ liệu; có tính mô tả cao nhưng nặng hơn JSON — sử dụng thẻ lồng nhau</v>
+        <v>XML tự động mã hóa dữ liệu thành hình ảnh đồ họa 3D trước khi gửi đi — mã hóa hình ảnh</v>
       </c>
       <c r="G6" t="str">
         <v>XML chỉ lưu trữ được số nguyên còn JSON chỉ lưu trữ được chuỗi văn bản — giới hạn kiểu dữ liệu</v>
       </c>
       <c r="H6" t="str">
-        <v>XML tự động mã hóa dữ liệu thành hình ảnh đồ họa 3D trước khi gửi đi — mã hóa hình ảnh</v>
+        <v>Sử dụng các cặp thẻ lồng nhau (như &lt;the&gt;noi dung&lt;/the&gt;) để cấu trúc dữ liệu; có tính mô tả cao nhưng nặng hơn JSON — sử dụng thẻ lồng nhau</v>
       </c>
       <c r="I6" t="str">
         <v>XML bắt buộc phải chạy trên hệ điều hành Windows chứ không chạy được trên Linux — ràng buộc hệ điều hành</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Data Dictionary là tài liệu mô tả chi tiết siêu dữ liệu (metadata), định nghĩa rõ cấu trúc dữ liệu của các bảng (tên cột, kiểu dữ liệu: string/int, độ dài, khóa chính/khóa ngoại, mô tả ý nghĩa).</v>
       </c>
       <c r="F7" t="str">
+        <v>Liệt kê tất cả các tài khoản đăng nhập của người dùng trong hệ thống database — danh sách tài khoản</v>
+      </c>
+      <c r="G7" t="str">
         <v>Giải thích định nghĩa, kiểu dữ liệu, độ dài và ràng buộc của từng trường dữ liệu trong hệ thống — định nghĩa trường dữ liệu</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Dịch các câu lệnh SQL từ tiếng Anh sang tiếng Việt cho khách hàng đọc hiểu — dịch thuật SQL</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Liệt kê tất cả các tài khoản đăng nhập của người dùng trong hệ thống database — danh sách tài khoản</v>
       </c>
       <c r="I7" t="str">
         <v>Từ điển giải thích các thuật ngữ tiếng Anh chuyên ngành của dự án — từ điển thuật ngữ</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Khóa ngoại (Foreign Key) là cột trong một bảng trỏ đến khóa chính (Primary Key) của bảng khác, dùng để thiết lập mối liên kết dữ liệu giữa các thực thể.</v>
       </c>
       <c r="F8" t="str">
+        <v>Dùng để đảm bảo giá trị trong cột đó là duy nhất và không được trùng lặp trong cùng một bảng — khóa duy nhất</v>
+      </c>
+      <c r="G8" t="str">
         <v>Dùng để liên kết một bảng này với bảng khác bằng cách trỏ tới khóa chính của bảng được liên kết — thiết lập quan hệ liên kết</v>
       </c>
-      <c r="G8" t="str">
-        <v>Dùng để đảm bảo giá trị trong cột đó là duy nhất và không được trùng lặp trong cùng một bảng — khóa duy nhất</v>
-      </c>
       <c r="H8" t="str">
+        <v>Dùng để mã hóa mật khẩu người dùng trước khi lưu trữ vào database — khóa mật khẩu</v>
+      </c>
+      <c r="I8" t="str">
         <v>Dùng để tự động tăng giá trị của trường số nguyên lên 1 đơn vị khi thêm hàng mới — tự động tăng</v>
       </c>
-      <c r="I8" t="str">
-        <v>Dùng để mã hóa mật khẩu người dùng trước khi lưu trữ vào database — khóa mật khẩu</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Đầu số HTTP 2xx biểu thị sự thành công. Status Code 200 OK là mã phản hồi chuẩn cho thấy request đã được xử lý thành công.</v>
       </c>
       <c r="F9" t="str">
+        <v>Máy chủ gặp lỗi xử lý logic nội bộ và không thể trả về dữ liệu — lỗi máy chủ</v>
+      </c>
+      <c r="G9" t="str">
         <v>Yêu cầu đã được tiếp nhận và xử lý thành công từ phía máy chủ — thành công</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Yêu cầu bị từ chối vì tài khoản của người dùng không có quyền truy cập — lỗi phân quyền</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Không tìm thấy địa chỉ URL của API trên máy chủ — không tìm thấy tài nguyên</v>
       </c>
-      <c r="I9" t="str">
-        <v>Máy chủ gặp lỗi xử lý logic nội bộ và không thể trả về dữ liệu — lỗi máy chủ</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Một dòng ở bảng A có thể liên kết với nhiều dòng ở bảng B, nhưng một dòng ở bảng B chỉ liên kết với tối đa một dòng ở bảng A — quan hệ một nhiều</v>
       </c>
       <c r="G10" t="str">
-        <v>Một dòng ở bảng A chỉ liên kết với đúng một dòng ở bảng B và ngược lại — quan hệ một một</v>
+        <v>Một bảng chỉ được phép chứa tối đa 1 cột khóa chính và n cột khóa ngoại — giới hạn số cột</v>
       </c>
       <c r="H10" t="str">
         <v>Nhiều dòng ở bảng A có thể tự do liên kết với nhiều dòng ở bảng B mà không có ràng buộc nào — quan hệ nhiều nhiều</v>
       </c>
       <c r="I10" t="str">
-        <v>Một bảng chỉ được phép chứa tối đa 1 cột khóa chính và n cột khóa ngoại — giới hạn số cột</v>
+        <v>Một dòng ở bảng A chỉ liên kết với đúng một dòng ở bảng B và ngược lại — quan hệ một một</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>Data Mapping là quá trình thiết lập mối liên kết giữa các trường dữ liệu ở bảng nguồn (Source) và bảng đích (Target) phục vụ tích hợp hoặc chuyển đổi dữ liệu.</v>
       </c>
       <c r="F11" t="str">
+        <v>Vẽ bản đồ sơ đồ mạng kết nối các máy chủ vật lý của hai công ty lại với nhau — sơ đồ hạ tầng</v>
+      </c>
+      <c r="G11" t="str">
         <v>Xác định trường dữ liệu tương ứng giữa hai hệ thống để đảm bảo dữ liệu truyền đi đúng vị trí và không bị mất mát — ánh xạ cột dữ liệu</v>
       </c>
-      <c r="G11" t="str">
-        <v>Vẽ bản đồ sơ đồ mạng kết nối các máy chủ vật lý của hai công ty lại với nhau — sơ đồ hạ tầng</v>
-      </c>
       <c r="H11" t="str">
+        <v>Dịch giao diện phần mềm của hệ thống cũ sang ngôn ngữ của hệ thống mới — dịch giao diện</v>
+      </c>
+      <c r="I11" t="str">
         <v>Xóa bỏ toàn bộ dữ liệu trùng lặp trên ổ cứng của máy chủ lưu trữ — dọn dẹp bộ nhớ</v>
       </c>
-      <c r="I11" t="str">
-        <v>Dịch giao diện phần mềm của hệ thống cũ sang ngôn ngữ của hệ thống mới — dịch giao diện</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
